--- a/tools/excel_export/excel/shop_constants.xlsx
+++ b/tools/excel_export/excel/shop_constants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>key</t>
   </si>
@@ -67,6 +67,9 @@
     <t>drawCostStep</t>
   </si>
   <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>每次抽取后的费用增量（金币）</t>
   </si>
   <si>
@@ -76,7 +79,7 @@
     <t>200</t>
   </si>
   <si>
-    <t>抽取费用上限（金币）；到达后保持不再增长</t>
+    <t>抽取费用上限（金币）；到达后保持不再增长（0 = 不封顶）</t>
   </si>
   <si>
     <t>drawCostResetEachPhase</t>
@@ -97,82 +100,109 @@
     <t>各阶段可抽取的最高 stage（数组，索引 0 = 阶段 1）；越阶判定见 shop_draw.upgrade_chance</t>
   </si>
   <si>
-    <t>relicSkillPoolWeight</t>
-  </si>
-  <si>
-    <t>{"relic":1,"skill":1}</t>
+    <t>skillMaxPerDraw</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>每次抽取里的技能选项数上限（0~2：抽到的技能个数不会超过它；0 = 永不出技能）</t>
+  </si>
+  <si>
+    <t>skillDrawChance</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>每次抽取「出技能」的概率 %（默认 20 = 20% 有技能 / 80% 一个技能都不出）；品质概率不受它影响</t>
+  </si>
+  <si>
+    <t>skillCountWeight</t>
+  </si>
+  <si>
+    <t>{"1":70,"2":30}</t>
+  </si>
+  <si>
+    <t>出技能时抽到几个的权重（{"1":70,"2":30} = 1 个 70% / 2 个 30%；只认 1 ~ skillMaxPerDraw 的键，未配即 1 个）</t>
+  </si>
+  <si>
+    <t>duplicateSkillUpgrade</t>
+  </si>
+  <si>
+    <t>抽到已拥有技能时是否转为升级（1=是，满级后不可选；0=不可选）</t>
+  </si>
+  <si>
+    <t>maxSkillSlots</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>技能槽上限（技能型选项超过该数量后不可再选新技能）</t>
+  </si>
+  <si>
+    <t>adFreeDrawEnabled</t>
+  </si>
+  <si>
+    <t>是否开放「看广告免费抽一次」（1=开放）</t>
+  </si>
+  <si>
+    <t>adFreeDrawPerRun</t>
+  </si>
+  <si>
+    <t>每局广告免费抽取次数上限</t>
+  </si>
+  <si>
+    <t>adExtraPickEnabled</t>
+  </si>
+  <si>
+    <t>是否开放「看广告额外选 1 个」（1=开放；在本次已置灰的选项中再选 1 个）</t>
+  </si>
+  <si>
+    <t>adExtraPickCount</t>
+  </si>
+  <si>
+    <t>广告额外可选的选项数</t>
+  </si>
+  <si>
+    <t>adRefreshEnabled</t>
+  </si>
+  <si>
+    <t>是否开放「看广告免费刷新本次抽取」（1=开放，重抽但选项数不变）</t>
+  </si>
+  <si>
+    <t>killBuffPriceGrowth</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>击杀商店 Buff 默认价格系数（单个 Buff 的 price_growth 优先）</t>
+  </si>
+  <si>
+    <t>killBuffMaxStackDefault</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>击杀商店 Buff 默认层数上限（单个 Buff 的 max_stack 优先）</t>
+  </si>
+  <si>
+    <t>killBuffRefreshCost</t>
+  </si>
+  <si>
+    <t>击杀商店刷新一次摊位的费用（单位 = **击杀数**，不是金币；金币只用于选英雄刷新与遗物抽取）</t>
+  </si>
+  <si>
+    <t>heroSelectRefreshCost</t>
+  </si>
+  <si>
+    <t>100</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>guaranteeSkillPerDraw</t>
-  </si>
-  <si>
-    <t>每次抽取至少包含的技能选项数（0 = 不保证）</t>
-  </si>
-  <si>
-    <t>duplicateSkillUpgrade</t>
-  </si>
-  <si>
-    <t>抽到已拥有技能时是否转为升级（1=是，满级后不可选；0=不可选）</t>
-  </si>
-  <si>
-    <t>maxSkillSlots</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>技能槽上限（技能型选项超过该数量后不可再选新技能）</t>
-  </si>
-  <si>
-    <t>adFreeDrawEnabled</t>
-  </si>
-  <si>
-    <t>是否开放「看广告免费抽一次」（1=开放）</t>
-  </si>
-  <si>
-    <t>adFreeDrawPerRun</t>
-  </si>
-  <si>
-    <t>每局广告免费抽取次数上限</t>
-  </si>
-  <si>
-    <t>adExtraPickEnabled</t>
-  </si>
-  <si>
-    <t>是否开放「看广告额外选 1 个」（1=开放；在本次已置灰的选项中再选 1 个）</t>
-  </si>
-  <si>
-    <t>adExtraPickCount</t>
-  </si>
-  <si>
-    <t>广告额外可选的选项数</t>
-  </si>
-  <si>
-    <t>adRefreshEnabled</t>
-  </si>
-  <si>
-    <t>是否开放「看广告免费刷新本次抽取」（1=开放，重抽但选项数不变）</t>
-  </si>
-  <si>
-    <t>killBuffPriceGrowth</t>
-  </si>
-  <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>击杀商店 Buff 默认价格系数（单个 Buff 的 price_growth 优先）</t>
-  </si>
-  <si>
-    <t>killBuffMaxStackDefault</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>击杀商店 Buff 默认层数上限（单个 Buff 的 max_stack 优先）</t>
   </si>
 </sst>
 </file>
@@ -612,7 +642,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25.5" customWidth="1"/>
@@ -691,164 +721,197 @@
         <v>17</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/tools/excel_export/excel/shop_constants.xlsx
+++ b/tools/excel_export/excel/shop_constants.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="72">
   <si>
     <t>key</t>
   </si>
@@ -76,124 +76,148 @@
     <t>drawCostCap</t>
   </si>
   <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>抽取费用上限（金币）；到达后保持不再增长（0 = 不封顶）</t>
+  </si>
+  <si>
+    <t>drawCostResetEachPhase</t>
+  </si>
+  <si>
+    <t>是否每阶段重置抽取次数（1=重置回 drawCostBase，0=整局累计）</t>
+  </si>
+  <si>
+    <t>stageMaxByPhase</t>
+  </si>
+  <si>
+    <t>[1,2,3,4]</t>
+  </si>
+  <si>
+    <t>各阶段可抽取的最高 stage（数组，索引 0 = 阶段 1）；越阶判定见 shop_draw.upgrade_chance</t>
+  </si>
+  <si>
+    <t>skillMaxPerDraw</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>每次抽取里的技能选项数上限（0~2：抽到的技能个数不会超过它；0 = 永不出技能）</t>
+  </si>
+  <si>
+    <t>skillDrawChance</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>每次抽取「出技能」的概率 %（默认 20 = 20% 有技能 / 80% 一个技能都不出）；品质概率不受它影响</t>
+  </si>
+  <si>
+    <t>skillCountWeight</t>
+  </si>
+  <si>
+    <t>{"1":70,"2":30}</t>
+  </si>
+  <si>
+    <t>出技能时抽到几个的权重（{"1":70,"2":30} = 1 个 70% / 2 个 30%；只认 1 ~ skillMaxPerDraw 的键，未配即 1 个）</t>
+  </si>
+  <si>
+    <t>duplicateSkillUpgrade</t>
+  </si>
+  <si>
+    <t>抽到已拥有技能时是否转为升级（1=是，满级后不可选；0=不可选）</t>
+  </si>
+  <si>
+    <t>maxSkillSlots</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>技能槽上限（技能型选项超过该数量后不可再选新技能）</t>
+  </si>
+  <si>
+    <t>adFreeDrawEnabled</t>
+  </si>
+  <si>
+    <t>是否开放「看广告免费抽一次」（1=开放）</t>
+  </si>
+  <si>
+    <t>adFreeDrawPerRun</t>
+  </si>
+  <si>
+    <t>每局广告免费抽取次数上限</t>
+  </si>
+  <si>
+    <t>adExtraPickEnabled</t>
+  </si>
+  <si>
+    <t>是否开放「看广告额外选 1 个」（1=开放；在本次已置灰的选项中再选 1 个）</t>
+  </si>
+  <si>
+    <t>adExtraPickCount</t>
+  </si>
+  <si>
+    <t>广告额外可选的选项数</t>
+  </si>
+  <si>
+    <t>adRefreshEnabled</t>
+  </si>
+  <si>
+    <t>是否开放「看广告免费刷新本次抽取」（1=开放，重抽但选项数不变）</t>
+  </si>
+  <si>
+    <t>killBuffPriceGrowth</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>神器默认价格系数（**同一件每买一层**的价格 ×；单个神器的 price_growth 优先）</t>
+  </si>
+  <si>
+    <t>killBuffMaxStackDefault</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>神器默认层数上限（单个神器的 max_stack 优先）</t>
+  </si>
+  <si>
+    <t>killBuffRefreshCost</t>
+  </si>
+  <si>
+    <t>击杀商店（神器）刷新一次摊位的**首次**费用（单位 = **击杀数**，不是金币；金币只用于选英雄刷新与遗物抽取）</t>
+  </si>
+  <si>
+    <t>killBuffRefreshCostStep</t>
+  </si>
+  <si>
+    <t>神器**付费刷新**每次递增的费用（击杀数）；免费刷新 / 广告刷新**不递增**（见 docs/artifact-drop/README.md §12）</t>
+  </si>
+  <si>
+    <t>killBuffRefreshCostCap</t>
+  </si>
+  <si>
     <t>200</t>
   </si>
   <si>
-    <t>抽取费用上限（金币）；到达后保持不再增长（0 = 不封顶）</t>
-  </si>
-  <si>
-    <t>drawCostResetEachPhase</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>是否每阶段重置抽取次数（1=重置回 drawCostBase，0=整局累计）</t>
-  </si>
-  <si>
-    <t>stageMaxByPhase</t>
-  </si>
-  <si>
-    <t>[1,2,3,4]</t>
-  </si>
-  <si>
-    <t>各阶段可抽取的最高 stage（数组，索引 0 = 阶段 1）；越阶判定见 shop_draw.upgrade_chance</t>
-  </si>
-  <si>
-    <t>skillMaxPerDraw</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>每次抽取里的技能选项数上限（0~2：抽到的技能个数不会超过它；0 = 永不出技能）</t>
-  </si>
-  <si>
-    <t>skillDrawChance</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>每次抽取「出技能」的概率 %（默认 20 = 20% 有技能 / 80% 一个技能都不出）；品质概率不受它影响</t>
-  </si>
-  <si>
-    <t>skillCountWeight</t>
-  </si>
-  <si>
-    <t>{"1":70,"2":30}</t>
-  </si>
-  <si>
-    <t>出技能时抽到几个的权重（{"1":70,"2":30} = 1 个 70% / 2 个 30%；只认 1 ~ skillMaxPerDraw 的键，未配即 1 个）</t>
-  </si>
-  <si>
-    <t>duplicateSkillUpgrade</t>
-  </si>
-  <si>
-    <t>抽到已拥有技能时是否转为升级（1=是，满级后不可选；0=不可选）</t>
-  </si>
-  <si>
-    <t>maxSkillSlots</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>技能槽上限（技能型选项超过该数量后不可再选新技能）</t>
-  </si>
-  <si>
-    <t>adFreeDrawEnabled</t>
-  </si>
-  <si>
-    <t>是否开放「看广告免费抽一次」（1=开放）</t>
-  </si>
-  <si>
-    <t>adFreeDrawPerRun</t>
-  </si>
-  <si>
-    <t>每局广告免费抽取次数上限</t>
-  </si>
-  <si>
-    <t>adExtraPickEnabled</t>
-  </si>
-  <si>
-    <t>是否开放「看广告额外选 1 个」（1=开放；在本次已置灰的选项中再选 1 个）</t>
-  </si>
-  <si>
-    <t>adExtraPickCount</t>
-  </si>
-  <si>
-    <t>广告额外可选的选项数</t>
-  </si>
-  <si>
-    <t>adRefreshEnabled</t>
-  </si>
-  <si>
-    <t>是否开放「看广告免费刷新本次抽取」（1=开放，重抽但选项数不变）</t>
-  </si>
-  <si>
-    <t>killBuffPriceGrowth</t>
-  </si>
-  <si>
-    <t>1.35</t>
-  </si>
-  <si>
-    <t>击杀商店 Buff 默认价格系数（单个 Buff 的 price_growth 优先）</t>
-  </si>
-  <si>
-    <t>killBuffMaxStackDefault</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>击杀商店 Buff 默认层数上限（单个 Buff 的 max_stack 优先）</t>
-  </si>
-  <si>
-    <t>killBuffRefreshCost</t>
-  </si>
-  <si>
-    <t>击杀商店刷新一次摊位的费用（单位 = **击杀数**，不是金币；金币只用于选英雄刷新与遗物抽取）</t>
+    <t>神器单次刷新费用上限（击杀数）；到达后保持不再增长（0 = 不封顶）。⚠ 刷新**次数**本身不封顶，封的只是单价</t>
+  </si>
+  <si>
+    <t>killBuffFreeRefreshPerRun</t>
+  </si>
+  <si>
+    <t>每局**开局白送**的神器免费刷新次数（不花击杀数、也不抬高后续单价）；0 = 不白送</t>
+  </si>
+  <si>
+    <t>killBuffRefreshAdFreePerRun</t>
+  </si>
+  <si>
+    <t>每局神器的「看广告免费刷新」次数（同样不抬高单价）；0 = 关掉这条通道。⚠ 这个键原先只在代码里当默认值（1），配表里没有 ⇒ 设计者改不动，2026-11 补上</t>
   </si>
   <si>
     <t>heroSelectRefreshCost</t>
@@ -202,7 +226,7 @@
     <t>100</t>
   </si>
   <si>
-    <t/>
+    <t>选英雄面板刷新一次候选的费用（金币）</t>
   </si>
 </sst>
 </file>
@@ -642,10 +666,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="25.5" customWidth="1"/>
+    <col min="1" max="1" width="29" customWidth="1"/>
     <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
@@ -743,175 +767,219 @@
         <v>23</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="C11" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="C12" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="C13" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B24" s="4" t="s">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="B25" s="4" t="s">
         <v>63</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
